--- a/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 7,56</t>
+          <t>1,9; 7,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,62; 10,97</t>
+          <t>4,66; 10,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,51</t>
+          <t>5,16; 12,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,64</t>
+          <t>0,1; 0,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,29</t>
+          <t>1,04; 6,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,96; 11,47</t>
+          <t>4,59; 11,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,39; 11,86</t>
+          <t>5,31; 11,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,5; 10,68</t>
+          <t>1,41; 10,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,69</t>
+          <t>1,99; 5,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,96</t>
+          <t>5,5; 10,32</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,02; 11,26</t>
+          <t>5,94; 10,81</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 5,63</t>
+          <t>0,78; 5,37</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,77</t>
+          <t>3,78; 8,01</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,67</t>
+          <t>4,87; 9,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,55</t>
+          <t>4,92; 9,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,77</t>
+          <t>2,91; 8,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 10,39</t>
+          <t>5,78; 10,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,83</t>
+          <t>3,68; 7,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 9,24</t>
+          <t>4,85; 9,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,19</t>
+          <t>1,9; 4,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,52</t>
+          <t>5,23; 8,63</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,77; 7,9</t>
+          <t>4,88; 7,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,5</t>
+          <t>5,45; 8,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,24</t>
+          <t>2,75; 6,11</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,64; 11,23</t>
+          <t>5,11; 11,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,9</t>
+          <t>2,04; 6,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,76</t>
+          <t>0,56; 3,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,92</t>
+          <t>2,47; 7,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,32; 9,88</t>
+          <t>4,15; 10,02</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 7,49</t>
+          <t>2,43; 7,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,0</t>
+          <t>2,37; 6,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,82</t>
+          <t>2,29; 6,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,23; 9,49</t>
+          <t>5,12; 9,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,81</t>
+          <t>2,71; 5,78</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,42</t>
+          <t>1,88; 4,54</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,83; 6,13</t>
+          <t>2,66; 6,13</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,98</t>
+          <t>0,97; 4,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,76</t>
+          <t>2,37; 6,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 11,39</t>
+          <t>5,48; 11,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,38</t>
+          <t>0,0; 0,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,12</t>
+          <t>1,87; 5,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,59</t>
+          <t>1,85; 5,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,96</t>
+          <t>3,57; 8,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,03</t>
+          <t>0,21; 1,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 4,45</t>
+          <t>1,88; 4,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 5,3</t>
+          <t>2,65; 5,5</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>4,79; 8,69</t>
+          <t>5,07; 9,27</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,16; 1,29</t>
+          <t>0,17; 1,15</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 7,07</t>
+          <t>1,29; 7,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,23</t>
+          <t>1,54; 7,25</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 6,01</t>
+          <t>1,07; 5,76</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,81; 9,7</t>
+          <t>2,62; 9,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,42; 9,66</t>
+          <t>3,47; 9,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,58; 6,3</t>
+          <t>1,59; 6,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,76</t>
+          <t>0,19; 3,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,44; 6,74</t>
+          <t>2,53; 6,76</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,41</t>
+          <t>3,22; 7,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 5,0</t>
+          <t>1,69; 4,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,49</t>
+          <t>0,13; 2,35</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,73</t>
+          <t>0,65; 4,75</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,47</t>
+          <t>0,72; 4,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,03</t>
+          <t>0,37; 3,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,93</t>
+          <t>0,92; 3,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,78</t>
+          <t>1,73; 6,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,06; 6,6</t>
+          <t>2,08; 6,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,42</t>
+          <t>0,91; 4,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,07</t>
+          <t>1,25; 4,09</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,55</t>
+          <t>1,77; 4,62</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,95</t>
+          <t>0,33; 1,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 3,46</t>
+          <t>1,2; 3,43</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,33</t>
+          <t>3,44; 7,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,58</t>
+          <t>3,08; 6,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,99</t>
+          <t>1,87; 5,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,51</t>
+          <t>2,6; 5,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,52; 11,43</t>
+          <t>6,57; 11,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,16; 11,72</t>
+          <t>7,29; 11,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,64</t>
+          <t>2,51; 5,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 5,29</t>
+          <t>1,49; 5,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,5</t>
+          <t>5,54; 8,53</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,69</t>
+          <t>5,62; 8,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,63</t>
+          <t>2,47; 4,59</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,89</t>
+          <t>2,22; 4,92</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,75</t>
+          <t>4,31; 7,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,09; 6,08</t>
+          <t>3,03; 5,97</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,39</t>
+          <t>1,68; 4,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,84</t>
+          <t>0,25; 1,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,38</t>
+          <t>3,94; 7,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,88; 8,48</t>
+          <t>4,83; 8,19</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,5</t>
+          <t>2,79; 5,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,34</t>
+          <t>0,78; 2,34</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,48; 6,89</t>
+          <t>4,55; 7,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,79</t>
+          <t>4,34; 6,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,39</t>
+          <t>2,62; 4,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,67</t>
+          <t>0,55; 1,72</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,6</t>
+          <t>4,1; 5,73</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,11; 5,66</t>
+          <t>4,04; 5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,63; 5,08</t>
+          <t>3,6; 4,98</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,07</t>
+          <t>1,63; 2,92</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 6,9</t>
+          <t>5,14; 6,86</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,43; 7,05</t>
+          <t>5,38; 7,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,34</t>
+          <t>3,92; 5,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,92; 3,13</t>
+          <t>1,89; 3,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,86; 6,03</t>
+          <t>4,87; 6,02</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,92; 6,06</t>
+          <t>5,01; 6,05</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 4,93</t>
+          <t>3,93; 4,93</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,84</t>
+          <t>1,93; 2,84</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación</t>
+          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5090; 20628</t>
+          <t>5196; 20658</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13522; 32090</t>
+          <t>13643; 31788</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16774; 36637</t>
+          <t>15114; 37286</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>327; 2004</t>
+          <t>322; 1842</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2844; 16396</t>
+          <t>2712; 16617</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14047; 32454</t>
+          <t>12977; 31777</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15445; 33984</t>
+          <t>15207; 34186</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4339; 30946</t>
+          <t>4082; 29658</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10839; 30354</t>
+          <t>10603; 29977</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31775; 57343</t>
+          <t>31655; 59406</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34876; 65213</t>
+          <t>34428; 62593</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>5155; 33812</t>
+          <t>4681; 32257</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18229; 38313</t>
+          <t>18639; 39487</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25547; 48701</t>
+          <t>24497; 49591</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24394; 47794</t>
+          <t>24627; 49328</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15159; 45367</t>
+          <t>15028; 44353</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28957; 52373</t>
+          <t>29148; 53911</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19367; 40679</t>
+          <t>19149; 39632</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>23267; 48314</t>
+          <t>25380; 47963</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10532; 26570</t>
+          <t>9722; 25573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52640; 84902</t>
+          <t>52133; 86065</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48798; 80822</t>
+          <t>49958; 81514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53916; 86979</t>
+          <t>55796; 88563</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28661; 64235</t>
+          <t>28302; 62882</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14788; 35806</t>
+          <t>16294; 36003</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5899; 19117</t>
+          <t>6598; 19460</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1825; 11795</t>
+          <t>1765; 11804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7147; 24135</t>
+          <t>7522; 23242</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14477; 33148</t>
+          <t>13923; 33601</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8118; 25545</t>
+          <t>8270; 24894</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7799; 22976</t>
+          <t>7783; 22144</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7446; 23003</t>
+          <t>7711; 22376</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34186; 62102</t>
+          <t>33503; 61703</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>17516; 38656</t>
+          <t>18041; 38408</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12111; 28380</t>
+          <t>12100; 29186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18157; 39345</t>
+          <t>17085; 39375</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3379; 17811</t>
+          <t>3475; 16989</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>9273; 24914</t>
+          <t>8736; 24760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20214; 41951</t>
+          <t>20190; 42684</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1195</t>
+          <t>0; 1096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7105; 22731</t>
+          <t>6958; 21418</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7029; 21626</t>
+          <t>7167; 21551</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12703; 30844</t>
+          <t>13820; 32712</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1022; 9623</t>
+          <t>1002; 9408</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12636; 32415</t>
+          <t>13731; 32374</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19457; 40080</t>
+          <t>20019; 41533</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36198; 65672</t>
+          <t>38318; 70022</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1274; 10130</t>
+          <t>1336; 8994</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2701; 14131</t>
+          <t>2572; 15092</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4022; 15374</t>
+          <t>3266; 15417</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2668; 12566</t>
+          <t>2244; 12045</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 1225</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5670; 19567</t>
+          <t>5282; 19766</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7501; 21215</t>
+          <t>7621; 21608</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3427; 13718</t>
+          <t>3462; 13573</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>483; 9737</t>
+          <t>497; 8890</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>9787; 27053</t>
+          <t>10162; 27165</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13945; 32040</t>
+          <t>13924; 31248</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7128; 21349</t>
+          <t>7232; 20802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>554; 10892</t>
+          <t>588; 10262</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1053; 12760</t>
+          <t>1759; 12825</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1969; 12249</t>
+          <t>1976; 11316</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>963; 7965</t>
+          <t>964; 7911</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2497; 10566</t>
+          <t>2474; 10317</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4075; 16083</t>
+          <t>4808; 16825</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5736; 18410</t>
+          <t>5802; 18530</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 6513</t>
+          <t>0; 5599</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2339; 11355</t>
+          <t>2328; 11763</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7711; 22327</t>
+          <t>6847; 22407</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9195; 25133</t>
+          <t>9772; 25527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1844; 10431</t>
+          <t>1785; 10191</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6110; 18192</t>
+          <t>6334; 18014</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21741; 45027</t>
+          <t>21117; 43922</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20866; 43413</t>
+          <t>20291; 44188</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12894; 32461</t>
+          <t>12140; 32812</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15687; 33984</t>
+          <t>16037; 35935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41599; 72960</t>
+          <t>41951; 73683</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>49523; 81104</t>
+          <t>50450; 81217</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17432; 38716</t>
+          <t>17252; 38202</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>13364; 44558</t>
+          <t>12567; 43886</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>66954; 106467</t>
+          <t>69366; 106814</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>77068; 117413</t>
+          <t>75937; 114798</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34301; 61814</t>
+          <t>32945; 61402</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>33479; 71314</t>
+          <t>32402; 71743</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31888; 57342</t>
+          <t>31893; 56256</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>24098; 47336</t>
+          <t>23616; 46484</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>14409; 34107</t>
+          <t>13068; 32604</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1825; 17021</t>
+          <t>2264; 17057</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30302; 57588</t>
+          <t>30726; 56271</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>40153; 69774</t>
+          <t>39770; 67347</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23242; 45341</t>
+          <t>23005; 46660</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>6069; 16525</t>
+          <t>5506; 16570</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>68079; 104756</t>
+          <t>69139; 106637</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70937; 108746</t>
+          <t>69517; 108067</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>39995; 70358</t>
+          <t>41994; 73039</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>9183; 27175</t>
+          <t>8899; 27971</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>132020; 183004</t>
+          <t>133944; 187136</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>140369; 193221</t>
+          <t>137796; 188694</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>122364; 171312</t>
+          <t>121449; 167990</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56636; 105425</t>
+          <t>56103; 100191</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>174184; 232663</t>
+          <t>173320; 231291</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>192329; 250007</t>
+          <t>190703; 249600</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>136608; 188378</t>
+          <t>138065; 189847</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>70590; 114945</t>
+          <t>69417; 114009</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>322844; 400050</t>
+          <t>323144; 399602</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>342485; 421320</t>
+          <t>348380; 421226</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>270698; 340004</t>
+          <t>270888; 339895</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>137769; 201908</t>
+          <t>136957; 201799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,9; 7,57</t>
+          <t>1,96; 7,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,66; 10,86</t>
+          <t>4,8; 11,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,16; 12,74</t>
+          <t>5,45; 12,57</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,59</t>
+          <t>0,57; 3,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 6,37</t>
+          <t>1,05; 6,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,59; 11,23</t>
+          <t>4,67; 11,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,31; 11,93</t>
+          <t>5,42; 11,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,41; 10,24</t>
+          <t>2,05; 7,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,62</t>
+          <t>2,04; 5,61</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5,5; 10,32</t>
+          <t>5,49; 10,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,81</t>
+          <t>6,09; 11,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,37</t>
+          <t>1,57; 5,07</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,01</t>
+          <t>3,91; 8,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,87; 9,85</t>
+          <t>4,87; 9,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,92; 9,85</t>
+          <t>4,83; 9,62</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 8,57</t>
+          <t>2,93; 8,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,7</t>
+          <t>6,01; 10,58</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,68; 7,63</t>
+          <t>3,91; 7,85</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,85; 9,17</t>
+          <t>4,67; 9,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,99</t>
+          <t>2,83; 6,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 8,63</t>
+          <t>5,38; 8,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,88; 7,97</t>
+          <t>4,72; 7,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,45; 8,65</t>
+          <t>5,33; 8,62</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,11</t>
+          <t>3,25; 6,26</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,29</t>
+          <t>4,84; 11,26</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,01</t>
+          <t>1,79; 6,19</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,76</t>
+          <t>0,57; 3,92</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,47; 7,63</t>
+          <t>2,59; 7,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,02</t>
+          <t>4,27; 9,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,3</t>
+          <t>2,67; 7,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,74</t>
+          <t>2,54; 6,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 6,63</t>
+          <t>2,83; 7,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,12; 9,43</t>
+          <t>5,21; 9,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,78</t>
+          <t>2,69; 5,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,54</t>
+          <t>1,87; 4,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,66; 6,13</t>
+          <t>3,25; 6,7</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,75</t>
+          <t>1,12; 4,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 6,71</t>
+          <t>2,38; 6,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,48; 11,59</t>
+          <t>5,34; 11,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,35</t>
+          <t>0,0; 3,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,77</t>
+          <t>1,96; 5,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,85; 5,57</t>
+          <t>1,89; 5,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,57; 8,45</t>
+          <t>3,28; 8,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,99</t>
+          <t>0,46; 2,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,44</t>
+          <t>1,93; 4,64</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 5,5</t>
+          <t>2,57; 5,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 9,27</t>
+          <t>4,83; 8,6</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,15</t>
+          <t>0,51; 2,18</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,55</t>
+          <t>1,37; 7,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,25</t>
+          <t>1,66; 7,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,76</t>
+          <t>0,9; 5,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 9,8</t>
+          <t>2,61; 9,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,47; 9,84</t>
+          <t>3,55; 9,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,24</t>
+          <t>1,6; 6,27</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 3,44</t>
+          <t>0,19; 1,95</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 6,76</t>
+          <t>2,54; 6,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 7,23</t>
+          <t>3,32; 7,18</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,87</t>
+          <t>1,72; 5,1</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,13; 2,35</t>
+          <t>0,1; 1,05</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,75</t>
+          <t>0,65; 4,74</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,13</t>
+          <t>0,72; 4,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,01</t>
+          <t>0,36; 3,02</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,84</t>
+          <t>1,76; 6,73</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,73; 6,05</t>
+          <t>1,45; 5,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 6,64</t>
+          <t>2,06; 6,33</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,58</t>
+          <t>1,28; 4,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,09</t>
+          <t>1,41; 4,22</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,62</t>
+          <t>1,75; 4,53</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,9</t>
+          <t>0,35; 1,9</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,43</t>
+          <t>1,89; 4,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,15</t>
+          <t>3,58; 7,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,08; 6,7</t>
+          <t>3,07; 6,56</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 5,05</t>
+          <t>1,89; 4,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,83</t>
+          <t>2,79; 6,08</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 11,55</t>
+          <t>6,51; 11,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 11,74</t>
+          <t>7,12; 11,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,51; 5,57</t>
+          <t>2,5; 5,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,21</t>
+          <t>3,64; 6,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,54; 8,53</t>
+          <t>5,22; 8,37</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,62; 8,5</t>
+          <t>5,71; 8,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,59</t>
+          <t>2,5; 4,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,92</t>
+          <t>3,58; 5,75</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,31; 7,6</t>
+          <t>4,28; 7,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,97</t>
+          <t>3,02; 6,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,2</t>
+          <t>1,76; 4,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 1,85</t>
+          <t>0,43; 2,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,21</t>
+          <t>3,9; 7,24</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,83; 8,19</t>
+          <t>4,84; 8,37</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,79; 5,66</t>
+          <t>2,79; 5,61</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 2,34</t>
+          <t>1,2; 2,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,01</t>
+          <t>4,53; 6,89</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,75</t>
+          <t>4,37; 6,75</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,56</t>
+          <t>2,47; 4,45</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,72</t>
+          <t>0,95; 2,22</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4,1; 5,73</t>
+          <t>4,08; 5,69</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,04; 5,53</t>
+          <t>4,1; 5,51</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,6; 4,98</t>
+          <t>3,6; 5,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,92</t>
+          <t>2,18; 3,38</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,14; 6,86</t>
+          <t>5,18; 6,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38; 7,04</t>
+          <t>5,45; 7,07</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,92; 5,38</t>
+          <t>3,85; 5,27</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,1</t>
+          <t>2,75; 3,9</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,87; 6,02</t>
+          <t>4,81; 5,94</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,05</t>
+          <t>4,95; 6,06</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,93; 4,93</t>
+          <t>3,91; 4,93</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,93; 2,84</t>
+          <t>2,63; 3,45</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>4726</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>11089</t>
+          <t>13000</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11933</t>
+          <t>17726</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5196; 20658</t>
+          <t>5339; 20128</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13643; 31788</t>
+          <t>14037; 32613</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15114; 37286</t>
+          <t>15956; 36811</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>322; 1842</t>
+          <t>1807; 10403</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2712; 16617</t>
+          <t>2738; 15903</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12977; 31777</t>
+          <t>13217; 31323</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15207; 34186</t>
+          <t>15531; 34094</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4082; 29658</t>
+          <t>6464; 24573</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10603; 29977</t>
+          <t>10864; 29962</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>31655; 59406</t>
+          <t>31588; 58164</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>34428; 62593</t>
+          <t>35275; 64601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4681; 32257</t>
+          <t>9972; 32182</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25648</t>
+          <t>26232</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>23289</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41541</t>
+          <t>49520</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18639; 39487</t>
+          <t>19294; 40436</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>24497; 49591</t>
+          <t>24532; 49661</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>24627; 49328</t>
+          <t>24178; 48176</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15028; 44353</t>
+          <t>15497; 42774</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29148; 53911</t>
+          <t>30263; 53333</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19149; 39632</t>
+          <t>20315; 40784</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25380; 47963</t>
+          <t>24454; 48035</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9722; 25573</t>
+          <t>15372; 35862</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52133; 86065</t>
+          <t>53686; 84629</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49958; 81514</t>
+          <t>48308; 81579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>55796; 88563</t>
+          <t>54576; 88207</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>28302; 62882</t>
+          <t>34826; 67134</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13924</t>
+          <t>14802</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13443</t>
+          <t>16395</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27367</t>
+          <t>31197</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16294; 36003</t>
+          <t>15423; 35901</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6598; 19460</t>
+          <t>5816; 20073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1765; 11804</t>
+          <t>1786; 12299</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7522; 23242</t>
+          <t>7904; 24140</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13923; 33601</t>
+          <t>14313; 33037</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8270; 24894</t>
+          <t>9088; 25514</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7783; 22144</t>
+          <t>8356; 22658</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7711; 22376</t>
+          <t>9742; 25923</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33503; 61703</t>
+          <t>34118; 61772</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18041; 38408</t>
+          <t>17873; 38597</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12100; 29186</t>
+          <t>12024; 28591</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>17085; 39375</t>
+          <t>21088; 43485</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3742</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>8711</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3475; 16989</t>
+          <t>3993; 17416</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8736; 24760</t>
+          <t>8784; 25656</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20190; 42684</t>
+          <t>19678; 42992</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 1096</t>
+          <t>0; 12082</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6958; 21418</t>
+          <t>7289; 22053</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7167; 21551</t>
+          <t>7318; 22970</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13820; 32712</t>
+          <t>12717; 31444</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1002; 9408</t>
+          <t>1921; 11638</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>13731; 32374</t>
+          <t>14053; 33818</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>20019; 41533</t>
+          <t>19416; 40911</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38318; 70022</t>
+          <t>36487; 65005</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1336; 8994</t>
+          <t>4034; 17268</t>
         </is>
       </c>
     </row>
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1773</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2580</t>
+          <t>1773</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2572; 15092</t>
+          <t>2736; 14246</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3266; 15417</t>
+          <t>3526; 15099</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2244; 12045</t>
+          <t>1891; 11790</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5282; 19766</t>
+          <t>5272; 18898</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7621; 21608</t>
+          <t>7794; 21300</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3462; 13573</t>
+          <t>3471; 13650</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>497; 8890</t>
+          <t>442; 4471</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10162; 27165</t>
+          <t>10208; 27894</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13924; 31248</t>
+          <t>14343; 31012</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7232; 20802</t>
+          <t>7361; 21784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>588; 10262</t>
+          <t>443; 4567</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5452</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>5592</t>
+          <t>7206</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>16457</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1759; 12825</t>
+          <t>1744; 12798</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1976; 11316</t>
+          <t>1982; 11415</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>964; 7911</t>
+          <t>945; 7954</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2474; 10317</t>
+          <t>4741; 18157</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4808; 16825</t>
+          <t>4038; 15674</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5802; 18530</t>
+          <t>5745; 17670</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 5599</t>
+          <t>0; 6149</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2328; 11763</t>
+          <t>3370; 12736</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6847; 22407</t>
+          <t>7730; 23131</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>9772; 25527</t>
+          <t>9656; 25054</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1785; 10191</t>
+          <t>1855; 10161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6334; 18014</t>
+          <t>10093; 25293</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24246</t>
+          <t>29543</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>28794</t>
+          <t>38182</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>53040</t>
+          <t>67725</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21117; 43922</t>
+          <t>21958; 44500</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>20291; 44188</t>
+          <t>20226; 43266</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12140; 32812</t>
+          <t>12314; 31195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16037; 35935</t>
+          <t>19837; 43236</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41951; 73683</t>
+          <t>41543; 71764</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>50450; 81217</t>
+          <t>49273; 80269</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>17252; 38202</t>
+          <t>17130; 39467</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>12567; 43886</t>
+          <t>27767; 50267</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>69366; 106814</t>
+          <t>65407; 104872</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75937; 114798</t>
+          <t>77111; 115747</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>32945; 61402</t>
+          <t>33469; 60541</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32402; 71743</t>
+          <t>52858; 84742</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17261</t>
+          <t>23866</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>31893; 56256</t>
+          <t>31640; 58135</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23616; 46484</t>
+          <t>23500; 47830</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>13068; 32604</t>
+          <t>13659; 33511</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2264; 17057</t>
+          <t>3437; 18007</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>30726; 56271</t>
+          <t>30469; 56546</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39770; 67347</t>
+          <t>39851; 68840</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23005; 46660</t>
+          <t>23050; 46309</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>5506; 16570</t>
+          <t>9870; 24310</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69139; 106637</t>
+          <t>68919; 104780</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69517; 108067</t>
+          <t>70020; 108181</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>41994; 73039</t>
+          <t>39515; 71288</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8899; 27971</t>
+          <t>15334; 35836</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>77848</t>
+          <t>96365</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>90986</t>
+          <t>120611</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>168834</t>
+          <t>216975</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>133944; 187136</t>
+          <t>133114; 185742</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>137796; 188694</t>
+          <t>139961; 188220</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>121449; 167990</t>
+          <t>121365; 171510</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>56103; 100191</t>
+          <t>76391; 118263</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>173320; 231291</t>
+          <t>174603; 230064</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>190703; 249600</t>
+          <t>193119; 250564</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>138065; 189847</t>
+          <t>135844; 185701</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>69417; 114009</t>
+          <t>101730; 144358</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>323144; 399602</t>
+          <t>319328; 394110</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>348380; 421226</t>
+          <t>344656; 421901</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>270888; 339895</t>
+          <t>270054; 339993</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>136957; 201799</t>
+          <t>189584; 248382</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/Hacinamiento_R-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
+          <t>Población en cuya vivienda residen dos o más personas por habitación (tasa de respuesta: 99,44%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
